--- a/generation_zy/hiwo-任务2-1.xlsx
+++ b/generation_zy/hiwo-任务2-1.xlsx
@@ -397,7 +397,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="55">
   <si>
     <t>*金属板编号</t>
   </si>
@@ -495,7 +495,7 @@
     <t>等待</t>
   </si>
   <si>
-    <t>不关盖</t>
+    <t>关盖</t>
   </si>
   <si>
     <t>分钟</t>
@@ -504,7 +504,7 @@
     <t>RPM</t>
   </si>
   <si>
-    <t>不开盖</t>
+    <t>开盖</t>
   </si>
   <si>
     <t>次</t>
@@ -541,6 +541,12 @@
   </si>
   <si>
     <t>金属板编号</t>
+  </si>
+  <si>
+    <t>SS-A03</t>
+  </si>
+  <si>
+    <t>A05</t>
   </si>
   <si>
     <t>B03-1</t>
@@ -2033,7 +2039,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>30</v>
@@ -2046,19 +2052,19 @@
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="L3" s="2">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>34</v>
       </c>
       <c r="N3" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>33</v>
@@ -2102,7 +2108,9 @@
       <c r="AB3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AC3" s="2"/>
+      <c r="AC3" s="2">
+        <v>1</v>
+      </c>
       <c r="AD3" s="1" t="s">
         <v>33</v>
       </c>
@@ -2376,13 +2384,27 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>300</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" s="2"/>
@@ -2531,7 +2553,7 @@
     </row>
     <row r="2" spans="1:7" ht="15">
       <c r="A2" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -2543,13 +2565,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="2">
+        <v>190</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="2">
         <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="2">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
@@ -2699,25 +2721,25 @@
     </row>
     <row r="2" spans="1:7" ht="15">
       <c r="A2" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>1800</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>49</v>
       </c>
       <c r="G2" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
@@ -2867,25 +2889,25 @@
     </row>
     <row r="2" spans="1:7" ht="15">
       <c r="A2" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G2" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
@@ -3041,42 +3063,42 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G2" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G3" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
@@ -3284,13 +3306,13 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B56390C-5785-459D-955A-0626D2BDBAA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D4E9F9-586B-4C15-8B25-1081B498BAA4}">
   <dimension ref="A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="5" spans="1:1" ht="23.25" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
